--- a/Test-Data.xlsx
+++ b/Test-Data.xlsx
@@ -66,10 +66,10 @@
     <t>subulakshmi.Rajkumar@gmail</t>
   </si>
   <si>
-    <t>reshmamay6@gmail.com</t>
-  </si>
-  <si>
-    <t>resh12345</t>
+    <t>Subulakshmi.Rajkumar@gmail.com</t>
+  </si>
+  <si>
+    <t>subulakshmi123</t>
   </si>
 </sst>
 </file>
@@ -119,16 +119,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -435,9 +441,9 @@
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="3" width="32.005" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="3" width="32.71928571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="3" width="29.719285714285714" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="4" width="32.005" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="4" width="32.71928571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="5" width="29.719285714285714" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
@@ -447,18 +453,18 @@
       <c r="B1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>17</v>
       </c>
     </row>
@@ -475,23 +481,23 @@
   <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="3" width="26.433571428571426" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="3" width="29.719285714285714" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="3" width="30.290714285714284" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="3" width="32.29071428571429" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="4" width="26.433571428571426" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="5" width="29.719285714285714" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="5" width="30.290714285714284" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="5" width="32.29071428571429" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
     </row>
@@ -499,13 +505,13 @@
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>11</v>
       </c>
     </row>
@@ -522,23 +528,23 @@
   <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="3" width="26.719285714285714" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="3" width="25.433571428571426" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="3" width="28.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="3" width="27.719285714285714" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="4" width="26.719285714285714" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="5" width="25.433571428571426" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="5" width="28.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="5" width="27.719285714285714" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
     </row>
@@ -546,13 +552,13 @@
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>7</v>
       </c>
     </row>
